--- a/Data/Commodore-Repair-Toolbox.xlsx
+++ b/Data/Commodore-Repair-Toolbox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\Visual Studio\Commodore-Repair-Toolbox\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{108E6FE9-CCA3-494A-B15E-32598B6BD136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F671B3DE-DD10-46AF-B644-CE9CCB6E0A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hardware &amp; Board" sheetId="1" r:id="rId1"/>
@@ -171,7 +171,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-February-21</t>
+      <t>2026-March-2</t>
     </r>
   </si>
 </sst>
